--- a/artfynd/A 30326-2025 artfynd.xlsx
+++ b/artfynd/A 30326-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126016923</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126016924</v>
       </c>
       <c r="B3" t="n">
-        <v>97218</v>
+        <v>97222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30326-2025 artfynd.xlsx
+++ b/artfynd/A 30326-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>126016924</v>
       </c>
       <c r="B3" t="n">
-        <v>97222</v>
+        <v>97223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30326-2025 artfynd.xlsx
+++ b/artfynd/A 30326-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126016923</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126016924</v>
       </c>
       <c r="B3" t="n">
-        <v>97223</v>
+        <v>97225</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30326-2025 artfynd.xlsx
+++ b/artfynd/A 30326-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>126016924</v>
       </c>
       <c r="B3" t="n">
-        <v>97225</v>
+        <v>97227</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30326-2025 artfynd.xlsx
+++ b/artfynd/A 30326-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>126016924</v>
       </c>
       <c r="B3" t="n">
-        <v>97227</v>
+        <v>97229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30326-2025 artfynd.xlsx
+++ b/artfynd/A 30326-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126016923</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126016924</v>
       </c>
       <c r="B3" t="n">
-        <v>97229</v>
+        <v>97233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30326-2025 artfynd.xlsx
+++ b/artfynd/A 30326-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>126016924</v>
       </c>
       <c r="B3" t="n">
-        <v>97233</v>
+        <v>97236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30326-2025 artfynd.xlsx
+++ b/artfynd/A 30326-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126016923</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126016924</v>
       </c>
       <c r="B3" t="n">
-        <v>97236</v>
+        <v>97245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
